--- a/ACG_Common_Workbook.xlsx
+++ b/ACG_Common_Workbook.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acgworld-my.sharepoint.com/personal/shantanu_mule_acg-world_com/Documents/L4 Azure/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acgworld-my.sharepoint.com/personal/shantanu_mule_acg-world_com/Documents/L4 GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="11_17AEB7DF9ED093CE9E7EB73BF439FAF320B8E149" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9298E7EB-3ECC-40D4-9D85-95A046FDE440}"/>
+  <xr:revisionPtr revIDLastSave="167" documentId="11_17AEB7DF9ED093CE9E7EB73BF439FAF320B8E149" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C966F3A-7C0B-49DA-84C6-96EFE0A8F4A3}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6398" uniqueCount="1670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6397" uniqueCount="1669">
   <si>
     <t>URL</t>
   </si>
@@ -5043,9 +5043,6 @@
   </si>
   <si>
     <t>ACGSSCC_0108_10</t>
-  </si>
-  <si>
-    <t>B41A2B18:C35B18:C47A2B18:C35B18:B18:C35</t>
   </si>
   <si>
     <t>batman123@mailinator.com</t>
@@ -5714,7 +5711,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="22.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="56.453125" bestFit="1" customWidth="1"/>
@@ -5737,21 +5734,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="C2" s="15" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.35">
-      <c r="C18" t="s">
-        <v>1667</v>
       </c>
     </row>
   </sheetData>

--- a/ACG_Common_Workbook.xlsx
+++ b/ACG_Common_Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acgworld-my.sharepoint.com/personal/shantanu_mule_acg-world_com/Documents/L4 GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="167" documentId="11_17AEB7DF9ED093CE9E7EB73BF439FAF320B8E149" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C966F3A-7C0B-49DA-84C6-96EFE0A8F4A3}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="11_17AEB7DF9ED093CE9E7EB73BF439FAF320B8E149" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6073A2F0-1387-4AD2-BFB9-F3B8325D9D1E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6397" uniqueCount="1669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6397" uniqueCount="1668">
   <si>
     <t>URL</t>
   </si>
@@ -5046,9 +5046,6 @@
   </si>
   <si>
     <t>batman123@mailinator.com</t>
-  </si>
-  <si>
-    <t>https://lifesciencessit.acgi.in/</t>
   </si>
 </sst>
 </file>
@@ -5413,6 +5410,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -5734,7 +5735,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
-        <v>1668</v>
+        <v>1410</v>
       </c>
       <c r="B2" s="15" t="s">
         <v>1667</v>

--- a/ACG_Common_Workbook.xlsx
+++ b/ACG_Common_Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acgworld-my.sharepoint.com/personal/shantanu_mule_acg-world_com/Documents/L4 GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_00C8EA9AD50E0973F720971485755ACAFE86AB0A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D19A33C-8487-4878-86C9-D6ADAE77D9DB}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_00C8EA9AD50E0973F720971485755ACAFE86AB0A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DB7B075-8588-4DBA-AFC2-6315B28D2906}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5523,6 +5523,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
@@ -9532,7 +9536,7 @@
         <v>333</v>
       </c>
       <c r="X6" t="s">
-        <v>268</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
@@ -9576,7 +9580,7 @@
         <v>333</v>
       </c>
       <c r="X7" t="s">
-        <v>268</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
@@ -9620,7 +9624,7 @@
         <v>308</v>
       </c>
       <c r="W8" t="s">
-        <v>257</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.35">
@@ -9664,7 +9668,7 @@
         <v>308</v>
       </c>
       <c r="W9" t="s">
-        <v>257</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.35">

--- a/ACG_Common_Workbook.xlsx
+++ b/ACG_Common_Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acgworld-my.sharepoint.com/personal/shantanu_mule_acg-world_com/Documents/L4 GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_BC51649EEA57A95BDFF58069C04A1F5707F8277C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{743068DD-D57E-431F-88E9-810ABD8220F3}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_BC51649EEA57A95BDFF58069C04A1F5707F8277C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9F97A7C-2931-4620-963B-DC8F74E1622D}"/>
   <bookViews>
     <workbookView xWindow="4800" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4844,13 +4844,13 @@
     <t>https://172.16.70.187/?link=admins</t>
   </si>
   <si>
-    <t>betaenv@yopmail.com</t>
-  </si>
-  <si>
     <t>Test@12345</t>
   </si>
   <si>
-    <t>https://proud-mud-040601f00-beta.eastasia.4.azurestaticapps.net/login</t>
+    <t>https://proud-mud-040601f00-delta.eastasia.4.azurestaticapps.net/login</t>
+  </si>
+  <si>
+    <t>deltaenv@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -5534,13 +5534,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>1602</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="C2" s="15" t="s">
         <v>1600</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>1601</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>46</v>

--- a/ACG_Common_Workbook.xlsx
+++ b/ACG_Common_Workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acgworld-my.sharepoint.com/personal/shantanu_mule_acg-world_com/Documents/L4 GitHub/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_BC51649EEA57A95BDFF58069C04A1F5707F8277C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9F97A7C-2931-4620-963B-DC8F74E1622D}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_BC51649EEA57A95BDFF58069C04A1F5707F8277C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5289835A-1C37-4393-BD01-17DA02990285}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="3110" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="URL_Login_cred_Tenant" sheetId="1" r:id="rId1"/>
@@ -4844,13 +4844,13 @@
     <t>https://172.16.70.187/?link=admins</t>
   </si>
   <si>
-    <t>Test@12345</t>
-  </si>
-  <si>
-    <t>https://proud-mud-040601f00-delta.eastasia.4.azurestaticapps.net/login</t>
-  </si>
-  <si>
-    <t>deltaenv@yopmail.com</t>
+    <t>https://proud-mud-040601f00-gamma.eastasia.4.azurestaticapps.net/login</t>
+  </si>
+  <si>
+    <t>GammaTenant@mailinator.com</t>
+  </si>
+  <si>
+    <t>Acgi@1234</t>
   </si>
 </sst>
 </file>
@@ -5534,13 +5534,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>1601</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="C2" s="15" t="s">
         <v>1602</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>1600</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>46</v>
@@ -5549,8 +5549,8 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="B2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="C2" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B2" r:id="rId3" tooltip="mailto:gammatenant@mailinator.com" display="mailto:GammaTenant@mailinator.com" xr:uid="{AD30103F-2EF7-4ACD-8B23-031AE4F15A3E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
